--- a/pdfs/checklist-escavadeira.xlsx
+++ b/pdfs/checklist-escavadeira.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jdemitocombr-my.sharepoint.com/personal/dewid_dias_jdemito_com_br/Documents/Documents/Curso de Power BI/Documentos Dewid/TCC + ESTÁGIO/Atualização dos Checklist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1be6d7d730111a/Desktop/check/check/pdfs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{4AED1D8D-A0BA-43C5-A181-17D4B8EAFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55B5BD58-7EB1-4B83-972C-9968F18B48E3}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{4AED1D8D-A0BA-43C5-A181-17D4B8EAFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C1BFA90-BFA8-4423-BCE8-9D65C8D4B5B3}"/>
   <bookViews>
-    <workbookView xWindow="-4185" yWindow="-16320" windowWidth="29040" windowHeight="15840" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESCAVADEIRA" sheetId="75" r:id="rId1"/>
@@ -725,17 +725,17 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -817,10 +817,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -908,6 +908,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -917,8 +920,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -926,6 +935,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -951,102 +1047,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6181,6 +6181,158 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>22411</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>279586</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>262217</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="Grupo 201">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9BD01DC-76BD-42A2-AB06-24AE0882E74D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="9760323" y="7082117"/>
+          <a:ext cx="257175" cy="228600"/>
+          <a:chOff x="5939119" y="5076266"/>
+          <a:chExt cx="334745" cy="291352"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="Triângulo isósceles 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE070C52-11D1-5E08-A501-1525C5F69615}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5939119" y="5076266"/>
+            <a:ext cx="334745" cy="291352"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:endParaRPr lang="pt-BR" sz="3200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Britannic Bold" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="CaixaDeTexto 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E9D14EB-A4CE-C87D-DF57-63A8DE4AF99E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5995148" y="5109878"/>
+            <a:ext cx="173246" cy="257735"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1100" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="Bernard MT Condensed" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>!</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Bernard MT Condensed" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6975,8 +7127,8 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="19"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="52"/>
     </row>
     <row r="21" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="63" t="s">
@@ -7301,13 +7453,13 @@
       <c r="B37" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="86"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -7361,13 +7513,13 @@
       <c r="B40" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="84"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="85"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="86"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -7553,24 +7705,24 @@
       <c r="N49" s="52"/>
     </row>
     <row r="50" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="22">
+      <c r="A50" s="20">
         <v>35</v>
       </c>
-      <c r="B50" s="87" t="s">
+      <c r="B50" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="87"/>
-      <c r="D50" s="87"/>
-      <c r="E50" s="87"/>
-      <c r="F50" s="87"/>
-      <c r="G50" s="87"/>
-      <c r="H50" s="87"/>
-      <c r="I50" s="87"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="19"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="21"/>
     </row>
     <row r="51" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="63" t="s">
@@ -7654,16 +7806,16 @@
       <c r="A55" s="5">
         <v>39</v>
       </c>
-      <c r="B55" s="86" t="s">
+      <c r="B55" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="86"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
-      <c r="H55" s="86"/>
-      <c r="I55" s="86"/>
+      <c r="C55" s="87"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="87"/>
+      <c r="F55" s="87"/>
+      <c r="G55" s="87"/>
+      <c r="H55" s="87"/>
+      <c r="I55" s="87"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
@@ -7697,13 +7849,13 @@
       <c r="B57" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="C57" s="84"/>
-      <c r="D57" s="84"/>
-      <c r="E57" s="84"/>
-      <c r="F57" s="84"/>
-      <c r="G57" s="84"/>
-      <c r="H57" s="84"/>
-      <c r="I57" s="85"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="85"/>
+      <c r="E57" s="85"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="85"/>
+      <c r="I57" s="86"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
@@ -7717,13 +7869,13 @@
       <c r="B58" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="C58" s="84"/>
-      <c r="D58" s="84"/>
-      <c r="E58" s="84"/>
-      <c r="F58" s="84"/>
-      <c r="G58" s="84"/>
-      <c r="H58" s="84"/>
-      <c r="I58" s="85"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="85"/>
+      <c r="I58" s="86"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -7744,11 +7896,11 @@
       <c r="G59" s="67"/>
       <c r="H59" s="67"/>
       <c r="I59" s="68"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="21"/>
     </row>
     <row r="60" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="63" t="s">
@@ -7913,13 +8065,13 @@
       <c r="B68" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="88"/>
-      <c r="D68" s="88"/>
-      <c r="E68" s="88"/>
-      <c r="F68" s="88"/>
-      <c r="G68" s="88"/>
-      <c r="H68" s="88"/>
-      <c r="I68" s="89"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="91"/>
+      <c r="F68" s="91"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="91"/>
+      <c r="I68" s="92"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
@@ -7967,380 +8119,380 @@
       <c r="N70" s="52"/>
     </row>
     <row r="71" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="105" t="s">
+      <c r="A71" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B71" s="106"/>
-      <c r="C71" s="106"/>
-      <c r="D71" s="106"/>
-      <c r="E71" s="106"/>
-      <c r="F71" s="106"/>
-      <c r="G71" s="106"/>
-      <c r="H71" s="106"/>
-      <c r="I71" s="106"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="106"/>
-      <c r="L71" s="106"/>
-      <c r="M71" s="106"/>
-      <c r="N71" s="107"/>
+      <c r="B71" s="89"/>
+      <c r="C71" s="89"/>
+      <c r="D71" s="89"/>
+      <c r="E71" s="89"/>
+      <c r="F71" s="89"/>
+      <c r="G71" s="89"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="89"/>
+      <c r="J71" s="89"/>
+      <c r="K71" s="89"/>
+      <c r="L71" s="89"/>
+      <c r="M71" s="89"/>
+      <c r="N71" s="90"/>
     </row>
     <row r="72" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B72" s="91"/>
-      <c r="C72" s="91"/>
-      <c r="D72" s="91"/>
-      <c r="E72" s="91"/>
-      <c r="F72" s="91"/>
-      <c r="G72" s="91"/>
-      <c r="H72" s="91"/>
-      <c r="I72" s="91"/>
-      <c r="J72" s="91"/>
-      <c r="K72" s="91"/>
-      <c r="L72" s="91"/>
-      <c r="M72" s="91"/>
-      <c r="N72" s="92"/>
+      <c r="B72" s="123"/>
+      <c r="C72" s="123"/>
+      <c r="D72" s="123"/>
+      <c r="E72" s="123"/>
+      <c r="F72" s="123"/>
+      <c r="G72" s="123"/>
+      <c r="H72" s="123"/>
+      <c r="I72" s="123"/>
+      <c r="J72" s="123"/>
+      <c r="K72" s="123"/>
+      <c r="L72" s="123"/>
+      <c r="M72" s="123"/>
+      <c r="N72" s="124"/>
     </row>
     <row r="73" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="93" t="s">
+      <c r="A73" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="B73" s="94"/>
-      <c r="C73" s="94"/>
-      <c r="D73" s="94"/>
-      <c r="E73" s="94"/>
-      <c r="F73" s="94"/>
-      <c r="G73" s="94"/>
-      <c r="H73" s="94"/>
-      <c r="I73" s="94"/>
-      <c r="J73" s="94"/>
-      <c r="K73" s="94"/>
-      <c r="L73" s="94"/>
-      <c r="M73" s="94"/>
-      <c r="N73" s="95"/>
+      <c r="B73" s="126"/>
+      <c r="C73" s="126"/>
+      <c r="D73" s="126"/>
+      <c r="E73" s="126"/>
+      <c r="F73" s="126"/>
+      <c r="G73" s="126"/>
+      <c r="H73" s="126"/>
+      <c r="I73" s="126"/>
+      <c r="J73" s="126"/>
+      <c r="K73" s="126"/>
+      <c r="L73" s="126"/>
+      <c r="M73" s="126"/>
+      <c r="N73" s="127"/>
     </row>
     <row r="74" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="96" t="s">
+      <c r="A74" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="97"/>
-      <c r="C74" s="97"/>
-      <c r="D74" s="97"/>
-      <c r="E74" s="97"/>
-      <c r="F74" s="97"/>
-      <c r="G74" s="97"/>
-      <c r="H74" s="97"/>
-      <c r="I74" s="97"/>
-      <c r="J74" s="97"/>
-      <c r="K74" s="97"/>
-      <c r="L74" s="97"/>
-      <c r="M74" s="97"/>
-      <c r="N74" s="98"/>
+      <c r="B74" s="129"/>
+      <c r="C74" s="129"/>
+      <c r="D74" s="129"/>
+      <c r="E74" s="129"/>
+      <c r="F74" s="129"/>
+      <c r="G74" s="129"/>
+      <c r="H74" s="129"/>
+      <c r="I74" s="129"/>
+      <c r="J74" s="129"/>
+      <c r="K74" s="129"/>
+      <c r="L74" s="129"/>
+      <c r="M74" s="129"/>
+      <c r="N74" s="130"/>
     </row>
     <row r="75" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="96"/>
-      <c r="B75" s="97"/>
-      <c r="C75" s="97"/>
-      <c r="D75" s="97"/>
-      <c r="E75" s="97"/>
-      <c r="F75" s="97"/>
-      <c r="G75" s="97"/>
-      <c r="H75" s="97"/>
-      <c r="I75" s="97"/>
-      <c r="J75" s="97"/>
-      <c r="K75" s="97"/>
-      <c r="L75" s="97"/>
-      <c r="M75" s="97"/>
-      <c r="N75" s="98"/>
+      <c r="A75" s="128"/>
+      <c r="B75" s="129"/>
+      <c r="C75" s="129"/>
+      <c r="D75" s="129"/>
+      <c r="E75" s="129"/>
+      <c r="F75" s="129"/>
+      <c r="G75" s="129"/>
+      <c r="H75" s="129"/>
+      <c r="I75" s="129"/>
+      <c r="J75" s="129"/>
+      <c r="K75" s="129"/>
+      <c r="L75" s="129"/>
+      <c r="M75" s="129"/>
+      <c r="N75" s="130"/>
     </row>
     <row r="76" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="99"/>
-      <c r="B76" s="100"/>
-      <c r="C76" s="100"/>
-      <c r="D76" s="100"/>
-      <c r="E76" s="100"/>
-      <c r="F76" s="100"/>
-      <c r="G76" s="100"/>
-      <c r="H76" s="100"/>
-      <c r="I76" s="100"/>
-      <c r="J76" s="100"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="100"/>
-      <c r="N76" s="101"/>
+      <c r="A76" s="116"/>
+      <c r="B76" s="117"/>
+      <c r="C76" s="117"/>
+      <c r="D76" s="117"/>
+      <c r="E76" s="117"/>
+      <c r="F76" s="117"/>
+      <c r="G76" s="117"/>
+      <c r="H76" s="117"/>
+      <c r="I76" s="117"/>
+      <c r="J76" s="117"/>
+      <c r="K76" s="117"/>
+      <c r="L76" s="117"/>
+      <c r="M76" s="117"/>
+      <c r="N76" s="118"/>
     </row>
     <row r="77" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="102"/>
-      <c r="B77" s="103"/>
-      <c r="C77" s="103"/>
-      <c r="D77" s="103"/>
-      <c r="E77" s="103"/>
-      <c r="F77" s="103"/>
-      <c r="G77" s="103"/>
-      <c r="H77" s="103"/>
-      <c r="I77" s="103"/>
-      <c r="J77" s="103"/>
-      <c r="K77" s="103"/>
-      <c r="L77" s="103"/>
-      <c r="M77" s="103"/>
-      <c r="N77" s="104"/>
+      <c r="A77" s="119"/>
+      <c r="B77" s="120"/>
+      <c r="C77" s="120"/>
+      <c r="D77" s="120"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="120"/>
+      <c r="H77" s="120"/>
+      <c r="I77" s="120"/>
+      <c r="J77" s="120"/>
+      <c r="K77" s="120"/>
+      <c r="L77" s="120"/>
+      <c r="M77" s="120"/>
+      <c r="N77" s="121"/>
     </row>
     <row r="78" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="99"/>
-      <c r="B78" s="100"/>
-      <c r="C78" s="100"/>
-      <c r="D78" s="100"/>
-      <c r="E78" s="100"/>
-      <c r="F78" s="100"/>
-      <c r="G78" s="100"/>
-      <c r="H78" s="100"/>
-      <c r="I78" s="100"/>
-      <c r="J78" s="100"/>
-      <c r="K78" s="100"/>
-      <c r="L78" s="100"/>
-      <c r="M78" s="100"/>
-      <c r="N78" s="101"/>
+      <c r="A78" s="116"/>
+      <c r="B78" s="117"/>
+      <c r="C78" s="117"/>
+      <c r="D78" s="117"/>
+      <c r="E78" s="117"/>
+      <c r="F78" s="117"/>
+      <c r="G78" s="117"/>
+      <c r="H78" s="117"/>
+      <c r="I78" s="117"/>
+      <c r="J78" s="117"/>
+      <c r="K78" s="117"/>
+      <c r="L78" s="117"/>
+      <c r="M78" s="117"/>
+      <c r="N78" s="118"/>
     </row>
     <row r="79" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="102"/>
-      <c r="B79" s="103"/>
-      <c r="C79" s="103"/>
-      <c r="D79" s="103"/>
-      <c r="E79" s="103"/>
-      <c r="F79" s="103"/>
-      <c r="G79" s="103"/>
-      <c r="H79" s="103"/>
-      <c r="I79" s="103"/>
-      <c r="J79" s="103"/>
-      <c r="K79" s="103"/>
-      <c r="L79" s="103"/>
-      <c r="M79" s="103"/>
-      <c r="N79" s="104"/>
+      <c r="A79" s="119"/>
+      <c r="B79" s="120"/>
+      <c r="C79" s="120"/>
+      <c r="D79" s="120"/>
+      <c r="E79" s="120"/>
+      <c r="F79" s="120"/>
+      <c r="G79" s="120"/>
+      <c r="H79" s="120"/>
+      <c r="I79" s="120"/>
+      <c r="J79" s="120"/>
+      <c r="K79" s="120"/>
+      <c r="L79" s="120"/>
+      <c r="M79" s="120"/>
+      <c r="N79" s="121"/>
     </row>
     <row r="80" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="99"/>
-      <c r="B80" s="100"/>
-      <c r="C80" s="100"/>
-      <c r="D80" s="100"/>
-      <c r="E80" s="100"/>
-      <c r="F80" s="100"/>
-      <c r="G80" s="100"/>
-      <c r="H80" s="100"/>
-      <c r="I80" s="100"/>
-      <c r="J80" s="100"/>
-      <c r="K80" s="100"/>
-      <c r="L80" s="100"/>
-      <c r="M80" s="100"/>
-      <c r="N80" s="101"/>
+      <c r="A80" s="116"/>
+      <c r="B80" s="117"/>
+      <c r="C80" s="117"/>
+      <c r="D80" s="117"/>
+      <c r="E80" s="117"/>
+      <c r="F80" s="117"/>
+      <c r="G80" s="117"/>
+      <c r="H80" s="117"/>
+      <c r="I80" s="117"/>
+      <c r="J80" s="117"/>
+      <c r="K80" s="117"/>
+      <c r="L80" s="117"/>
+      <c r="M80" s="117"/>
+      <c r="N80" s="118"/>
     </row>
     <row r="81" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="102"/>
-      <c r="B81" s="103"/>
-      <c r="C81" s="103"/>
-      <c r="D81" s="103"/>
-      <c r="E81" s="103"/>
-      <c r="F81" s="103"/>
-      <c r="G81" s="103"/>
-      <c r="H81" s="103"/>
-      <c r="I81" s="103"/>
-      <c r="J81" s="103"/>
-      <c r="K81" s="103"/>
-      <c r="L81" s="103"/>
-      <c r="M81" s="103"/>
-      <c r="N81" s="104"/>
+      <c r="A81" s="119"/>
+      <c r="B81" s="120"/>
+      <c r="C81" s="120"/>
+      <c r="D81" s="120"/>
+      <c r="E81" s="120"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="120"/>
+      <c r="H81" s="120"/>
+      <c r="I81" s="120"/>
+      <c r="J81" s="120"/>
+      <c r="K81" s="120"/>
+      <c r="L81" s="120"/>
+      <c r="M81" s="120"/>
+      <c r="N81" s="121"/>
     </row>
     <row r="82" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="99"/>
-      <c r="B82" s="100"/>
-      <c r="C82" s="100"/>
-      <c r="D82" s="100"/>
-      <c r="E82" s="100"/>
-      <c r="F82" s="100"/>
-      <c r="G82" s="100"/>
-      <c r="H82" s="100"/>
-      <c r="I82" s="100"/>
-      <c r="J82" s="100"/>
-      <c r="K82" s="100"/>
-      <c r="L82" s="100"/>
-      <c r="M82" s="100"/>
-      <c r="N82" s="101"/>
+      <c r="A82" s="116"/>
+      <c r="B82" s="117"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="117"/>
+      <c r="E82" s="117"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="117"/>
+      <c r="J82" s="117"/>
+      <c r="K82" s="117"/>
+      <c r="L82" s="117"/>
+      <c r="M82" s="117"/>
+      <c r="N82" s="118"/>
     </row>
     <row r="83" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="102"/>
-      <c r="B83" s="103"/>
-      <c r="C83" s="103"/>
-      <c r="D83" s="103"/>
-      <c r="E83" s="103"/>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="103"/>
-      <c r="I83" s="103"/>
-      <c r="J83" s="103"/>
-      <c r="K83" s="103"/>
-      <c r="L83" s="103"/>
-      <c r="M83" s="103"/>
-      <c r="N83" s="104"/>
+      <c r="A83" s="119"/>
+      <c r="B83" s="120"/>
+      <c r="C83" s="120"/>
+      <c r="D83" s="120"/>
+      <c r="E83" s="120"/>
+      <c r="F83" s="120"/>
+      <c r="G83" s="120"/>
+      <c r="H83" s="120"/>
+      <c r="I83" s="120"/>
+      <c r="J83" s="120"/>
+      <c r="K83" s="120"/>
+      <c r="L83" s="120"/>
+      <c r="M83" s="120"/>
+      <c r="N83" s="121"/>
     </row>
     <row r="84" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="99"/>
-      <c r="B84" s="100"/>
-      <c r="C84" s="100"/>
-      <c r="D84" s="100"/>
-      <c r="E84" s="100"/>
-      <c r="F84" s="100"/>
-      <c r="G84" s="100"/>
-      <c r="H84" s="100"/>
-      <c r="I84" s="100"/>
-      <c r="J84" s="100"/>
-      <c r="K84" s="100"/>
-      <c r="L84" s="100"/>
-      <c r="M84" s="100"/>
-      <c r="N84" s="101"/>
+      <c r="A84" s="116"/>
+      <c r="B84" s="117"/>
+      <c r="C84" s="117"/>
+      <c r="D84" s="117"/>
+      <c r="E84" s="117"/>
+      <c r="F84" s="117"/>
+      <c r="G84" s="117"/>
+      <c r="H84" s="117"/>
+      <c r="I84" s="117"/>
+      <c r="J84" s="117"/>
+      <c r="K84" s="117"/>
+      <c r="L84" s="117"/>
+      <c r="M84" s="117"/>
+      <c r="N84" s="118"/>
     </row>
     <row r="85" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="102"/>
-      <c r="B85" s="103"/>
-      <c r="C85" s="103"/>
-      <c r="D85" s="103"/>
-      <c r="E85" s="103"/>
-      <c r="F85" s="103"/>
-      <c r="G85" s="103"/>
-      <c r="H85" s="103"/>
-      <c r="I85" s="103"/>
-      <c r="J85" s="103"/>
-      <c r="K85" s="103"/>
-      <c r="L85" s="103"/>
-      <c r="M85" s="103"/>
-      <c r="N85" s="104"/>
+      <c r="A85" s="119"/>
+      <c r="B85" s="120"/>
+      <c r="C85" s="120"/>
+      <c r="D85" s="120"/>
+      <c r="E85" s="120"/>
+      <c r="F85" s="120"/>
+      <c r="G85" s="120"/>
+      <c r="H85" s="120"/>
+      <c r="I85" s="120"/>
+      <c r="J85" s="120"/>
+      <c r="K85" s="120"/>
+      <c r="L85" s="120"/>
+      <c r="M85" s="120"/>
+      <c r="N85" s="121"/>
     </row>
     <row r="86" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="99"/>
-      <c r="B86" s="100"/>
-      <c r="C86" s="100"/>
-      <c r="D86" s="100"/>
-      <c r="E86" s="100"/>
-      <c r="F86" s="100"/>
-      <c r="G86" s="100"/>
-      <c r="H86" s="100"/>
-      <c r="I86" s="100"/>
-      <c r="J86" s="100"/>
-      <c r="K86" s="100"/>
-      <c r="L86" s="100"/>
-      <c r="M86" s="100"/>
-      <c r="N86" s="101"/>
+      <c r="A86" s="116"/>
+      <c r="B86" s="117"/>
+      <c r="C86" s="117"/>
+      <c r="D86" s="117"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="117"/>
+      <c r="H86" s="117"/>
+      <c r="I86" s="117"/>
+      <c r="J86" s="117"/>
+      <c r="K86" s="117"/>
+      <c r="L86" s="117"/>
+      <c r="M86" s="117"/>
+      <c r="N86" s="118"/>
     </row>
     <row r="87" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="102"/>
-      <c r="B87" s="103"/>
-      <c r="C87" s="103"/>
-      <c r="D87" s="103"/>
-      <c r="E87" s="103"/>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="103"/>
-      <c r="I87" s="103"/>
-      <c r="J87" s="103"/>
-      <c r="K87" s="103"/>
-      <c r="L87" s="103"/>
-      <c r="M87" s="103"/>
-      <c r="N87" s="104"/>
+      <c r="A87" s="119"/>
+      <c r="B87" s="120"/>
+      <c r="C87" s="120"/>
+      <c r="D87" s="120"/>
+      <c r="E87" s="120"/>
+      <c r="F87" s="120"/>
+      <c r="G87" s="120"/>
+      <c r="H87" s="120"/>
+      <c r="I87" s="120"/>
+      <c r="J87" s="120"/>
+      <c r="K87" s="120"/>
+      <c r="L87" s="120"/>
+      <c r="M87" s="120"/>
+      <c r="N87" s="121"/>
     </row>
     <row r="88" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="99"/>
-      <c r="B88" s="100"/>
-      <c r="C88" s="100"/>
-      <c r="D88" s="100"/>
-      <c r="E88" s="100"/>
-      <c r="F88" s="100"/>
-      <c r="G88" s="100"/>
-      <c r="H88" s="100"/>
-      <c r="I88" s="100"/>
-      <c r="J88" s="100"/>
-      <c r="K88" s="100"/>
-      <c r="L88" s="100"/>
-      <c r="M88" s="100"/>
-      <c r="N88" s="101"/>
+      <c r="A88" s="116"/>
+      <c r="B88" s="117"/>
+      <c r="C88" s="117"/>
+      <c r="D88" s="117"/>
+      <c r="E88" s="117"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="117"/>
+      <c r="H88" s="117"/>
+      <c r="I88" s="117"/>
+      <c r="J88" s="117"/>
+      <c r="K88" s="117"/>
+      <c r="L88" s="117"/>
+      <c r="M88" s="117"/>
+      <c r="N88" s="118"/>
     </row>
     <row r="89" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="102"/>
-      <c r="B89" s="103"/>
-      <c r="C89" s="103"/>
-      <c r="D89" s="103"/>
-      <c r="E89" s="103"/>
-      <c r="F89" s="103"/>
-      <c r="G89" s="103"/>
-      <c r="H89" s="103"/>
-      <c r="I89" s="103"/>
-      <c r="J89" s="103"/>
-      <c r="K89" s="103"/>
-      <c r="L89" s="103"/>
-      <c r="M89" s="103"/>
-      <c r="N89" s="104"/>
+      <c r="A89" s="119"/>
+      <c r="B89" s="120"/>
+      <c r="C89" s="120"/>
+      <c r="D89" s="120"/>
+      <c r="E89" s="120"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="120"/>
+      <c r="H89" s="120"/>
+      <c r="I89" s="120"/>
+      <c r="J89" s="120"/>
+      <c r="K89" s="120"/>
+      <c r="L89" s="120"/>
+      <c r="M89" s="120"/>
+      <c r="N89" s="121"/>
     </row>
     <row r="90" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="99"/>
-      <c r="B90" s="100"/>
-      <c r="C90" s="100"/>
-      <c r="D90" s="100"/>
-      <c r="E90" s="100"/>
-      <c r="F90" s="100"/>
-      <c r="G90" s="100"/>
-      <c r="H90" s="100"/>
-      <c r="I90" s="100"/>
-      <c r="J90" s="100"/>
-      <c r="K90" s="100"/>
-      <c r="L90" s="100"/>
-      <c r="M90" s="100"/>
-      <c r="N90" s="101"/>
+      <c r="A90" s="116"/>
+      <c r="B90" s="117"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="117"/>
+      <c r="E90" s="117"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="117"/>
+      <c r="J90" s="117"/>
+      <c r="K90" s="117"/>
+      <c r="L90" s="117"/>
+      <c r="M90" s="117"/>
+      <c r="N90" s="118"/>
     </row>
     <row r="91" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="102"/>
-      <c r="B91" s="103"/>
-      <c r="C91" s="103"/>
-      <c r="D91" s="103"/>
-      <c r="E91" s="103"/>
-      <c r="F91" s="103"/>
-      <c r="G91" s="103"/>
-      <c r="H91" s="103"/>
-      <c r="I91" s="103"/>
-      <c r="J91" s="103"/>
-      <c r="K91" s="103"/>
-      <c r="L91" s="103"/>
-      <c r="M91" s="103"/>
-      <c r="N91" s="104"/>
+      <c r="A91" s="119"/>
+      <c r="B91" s="120"/>
+      <c r="C91" s="120"/>
+      <c r="D91" s="120"/>
+      <c r="E91" s="120"/>
+      <c r="F91" s="120"/>
+      <c r="G91" s="120"/>
+      <c r="H91" s="120"/>
+      <c r="I91" s="120"/>
+      <c r="J91" s="120"/>
+      <c r="K91" s="120"/>
+      <c r="L91" s="120"/>
+      <c r="M91" s="120"/>
+      <c r="N91" s="121"/>
     </row>
     <row r="92" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="99"/>
-      <c r="B92" s="100"/>
-      <c r="C92" s="100"/>
-      <c r="D92" s="100"/>
-      <c r="E92" s="100"/>
-      <c r="F92" s="100"/>
-      <c r="G92" s="100"/>
-      <c r="H92" s="100"/>
-      <c r="I92" s="100"/>
-      <c r="J92" s="100"/>
-      <c r="K92" s="100"/>
-      <c r="L92" s="100"/>
-      <c r="M92" s="100"/>
-      <c r="N92" s="101"/>
+      <c r="A92" s="116"/>
+      <c r="B92" s="117"/>
+      <c r="C92" s="117"/>
+      <c r="D92" s="117"/>
+      <c r="E92" s="117"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+      <c r="I92" s="117"/>
+      <c r="J92" s="117"/>
+      <c r="K92" s="117"/>
+      <c r="L92" s="117"/>
+      <c r="M92" s="117"/>
+      <c r="N92" s="118"/>
     </row>
     <row r="93" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="102"/>
-      <c r="B93" s="103"/>
-      <c r="C93" s="103"/>
-      <c r="D93" s="103"/>
-      <c r="E93" s="103"/>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="103"/>
-      <c r="I93" s="103"/>
-      <c r="J93" s="103"/>
-      <c r="K93" s="103"/>
-      <c r="L93" s="103"/>
-      <c r="M93" s="103"/>
-      <c r="N93" s="104"/>
+      <c r="A93" s="119"/>
+      <c r="B93" s="120"/>
+      <c r="C93" s="120"/>
+      <c r="D93" s="120"/>
+      <c r="E93" s="120"/>
+      <c r="F93" s="120"/>
+      <c r="G93" s="120"/>
+      <c r="H93" s="120"/>
+      <c r="I93" s="120"/>
+      <c r="J93" s="120"/>
+      <c r="K93" s="120"/>
+      <c r="L93" s="120"/>
+      <c r="M93" s="120"/>
+      <c r="N93" s="121"/>
     </row>
     <row r="94" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="14"/>
@@ -8505,78 +8657,79 @@
       <c r="N103" s="7"/>
     </row>
     <row r="104" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="108" t="s">
+      <c r="A104" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B104" s="109"/>
-      <c r="C104" s="109"/>
-      <c r="D104" s="109"/>
-      <c r="E104" s="109"/>
-      <c r="F104" s="110"/>
+      <c r="B104" s="94"/>
+      <c r="C104" s="94"/>
+      <c r="D104" s="94"/>
+      <c r="E104" s="94"/>
+      <c r="F104" s="95"/>
       <c r="G104" s="18" t="s">
         <v>53</v>
       </c>
       <c r="H104" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I104" s="108" t="s">
+      <c r="I104" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="J104" s="109"/>
-      <c r="K104" s="110"/>
-      <c r="L104" s="108" t="s">
+      <c r="J104" s="94"/>
+      <c r="K104" s="95"/>
+      <c r="L104" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="M104" s="109"/>
-      <c r="N104" s="110"/>
+      <c r="M104" s="94"/>
+      <c r="N104" s="95"/>
     </row>
     <row r="105" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="111" t="s">
+      <c r="A105" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="B105" s="112"/>
-      <c r="C105" s="112"/>
-      <c r="D105" s="112"/>
-      <c r="E105" s="112"/>
-      <c r="F105" s="113"/>
-      <c r="G105" s="117" t="s">
+      <c r="B105" s="97"/>
+      <c r="C105" s="97"/>
+      <c r="D105" s="97"/>
+      <c r="E105" s="97"/>
+      <c r="F105" s="98"/>
+      <c r="G105" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="H105" s="113" t="s">
+      <c r="H105" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="I105" s="119">
+      <c r="I105" s="104">
         <v>45840</v>
       </c>
-      <c r="J105" s="120"/>
-      <c r="K105" s="121"/>
-      <c r="L105" s="125" t="s">
+      <c r="J105" s="105"/>
+      <c r="K105" s="106"/>
+      <c r="L105" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="M105" s="126"/>
-      <c r="N105" s="127"/>
+      <c r="M105" s="111"/>
+      <c r="N105" s="112"/>
     </row>
     <row r="106" spans="1:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="114"/>
-      <c r="B106" s="115"/>
-      <c r="C106" s="115"/>
-      <c r="D106" s="115"/>
-      <c r="E106" s="115"/>
-      <c r="F106" s="116"/>
-      <c r="G106" s="118"/>
-      <c r="H106" s="116"/>
-      <c r="I106" s="122"/>
-      <c r="J106" s="123"/>
-      <c r="K106" s="124"/>
-      <c r="L106" s="128"/>
-      <c r="M106" s="129"/>
-      <c r="N106" s="130"/>
+      <c r="A106" s="99"/>
+      <c r="B106" s="100"/>
+      <c r="C106" s="100"/>
+      <c r="D106" s="100"/>
+      <c r="E106" s="100"/>
+      <c r="F106" s="101"/>
+      <c r="G106" s="103"/>
+      <c r="H106" s="101"/>
+      <c r="I106" s="107"/>
+      <c r="J106" s="108"/>
+      <c r="K106" s="109"/>
+      <c r="L106" s="113"/>
+      <c r="M106" s="114"/>
+      <c r="N106" s="115"/>
       <c r="U106" s="1" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="160">
+    <mergeCell ref="M20:N20"/>
     <mergeCell ref="I7:N7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A7:D7"/>
@@ -8745,26 +8898,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b8015c9-aad1-4bac-8950-78e0ae91757b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="05331b14-7a17-452c-bd43-8b05eb5f4a9a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005D774826369C743B955A0E424486114" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b7648eedc9f31ac941a4e081c815f85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b8015c9-aad1-4bac-8950-78e0ae91757b" xmlns:ns3="05331b14-7a17-452c-bd43-8b05eb5f4a9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7515b1ab2e1a373f4dd779909eb5374a" ns2:_="" ns3:_="">
     <xsd:import namespace="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
@@ -8993,26 +9126,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C03874-9610-470E-BE88-5F3286AC6379}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64C91BFC-DF0B-44EF-9793-A743C907CDC7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
-    <ds:schemaRef ds:uri="05331b14-7a17-452c-bd43-8b05eb5f4a9a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b8015c9-aad1-4bac-8950-78e0ae91757b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="05331b14-7a17-452c-bd43-8b05eb5f4a9a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6103B53-A0F6-4640-A439-CB06EDC07A62}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9029,4 +9163,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C03874-9610-470E-BE88-5F3286AC6379}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64C91BFC-DF0B-44EF-9793-A743C907CDC7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
+    <ds:schemaRef ds:uri="05331b14-7a17-452c-bd43-8b05eb5f4a9a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>